--- a/Team-Data/2013-14/3-25-2013-14.xlsx
+++ b/Team-Data/2013-14/3-25-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -778,7 +845,7 @@
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>26</v>
@@ -942,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -972,7 +1039,7 @@
         <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV3" t="n">
         <v>22</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1139,7 +1206,7 @@
         <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
@@ -1157,7 +1224,7 @@
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>7</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1354,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
         <v>25</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -1467,16 +1534,16 @@
         <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>4</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
         <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>0.389</v>
+        <v>0.38</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
@@ -1589,40 +1656,40 @@
         <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84.5</v>
+        <v>84.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P7" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R7" t="n">
         <v>12.2</v>
       </c>
       <c r="S7" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
         <v>44.2</v>
       </c>
       <c r="U7" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V7" t="n">
         <v>14.5</v>
@@ -1631,7 +1698,7 @@
         <v>7.1</v>
       </c>
       <c r="X7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y7" t="n">
         <v>5.9</v>
@@ -1646,7 +1713,7 @@
         <v>97.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1661,7 +1728,7 @@
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1670,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>18</v>
@@ -1682,10 +1749,10 @@
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ7" t="n">
         <v>20</v>
@@ -1700,7 +1767,7 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -1718,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>0.597</v>
+        <v>0.592</v>
       </c>
       <c r="H8" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M8" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="N8" t="n">
         <v>0.382</v>
       </c>
       <c r="O8" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P8" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0.798</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S8" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U8" t="n">
         <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.2</v>
@@ -1822,13 +1889,13 @@
         <v>20.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>105</v>
+        <v>104.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1843,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1858,10 +1925,10 @@
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1900,7 +1967,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>5</v>
@@ -2243,7 +2310,7 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
         <v>8</v>
@@ -2401,7 +2468,7 @@
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2419,13 +2486,13 @@
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>9</v>
@@ -2446,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>5</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2789,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
@@ -2801,7 +2868,7 @@
         <v>26</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2935,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
         <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.343</v>
+        <v>0.333</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J15" t="n">
         <v>84.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L15" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.386</v>
+        <v>0.382</v>
       </c>
       <c r="O15" t="n">
         <v>17</v>
       </c>
       <c r="P15" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R15" t="n">
         <v>9.1</v>
@@ -3075,19 +3142,19 @@
         <v>32.2</v>
       </c>
       <c r="T15" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U15" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V15" t="n">
         <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y15" t="n">
         <v>4.7</v>
@@ -3099,13 +3166,13 @@
         <v>19.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.3</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.1</v>
+        <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3120,28 +3187,28 @@
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3165,7 +3232,7 @@
         <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -3174,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
@@ -3299,7 +3366,7 @@
         <v>9</v>
       </c>
       <c r="AH16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
@@ -3344,7 +3411,7 @@
         <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>4.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM17" t="n">
         <v>16</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3845,7 +3912,7 @@
         <v>16</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>11</v>
@@ -3872,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="n">
         <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>0.408</v>
+        <v>0.414</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.447</v>
@@ -4146,16 +4213,16 @@
         <v>9.1</v>
       </c>
       <c r="M21" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O21" t="n">
         <v>15.3</v>
       </c>
       <c r="P21" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0.755</v>
@@ -4164,16 +4231,16 @@
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T21" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W21" t="n">
         <v>7.6</v>
@@ -4185,7 +4252,7 @@
         <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.6</v>
@@ -4194,10 +4261,10 @@
         <v>98.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4209,7 +4276,7 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4218,10 +4285,10 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM21" t="n">
         <v>5</v>
@@ -4233,7 +4300,7 @@
         <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ21" t="n">
         <v>17</v>
@@ -4266,10 +4333,10 @@
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -4301,40 +4368,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
         <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.732</v>
+        <v>0.743</v>
       </c>
       <c r="H22" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J22" t="n">
-        <v>83</v>
+        <v>82.8</v>
       </c>
       <c r="K22" t="n">
         <v>0.471</v>
       </c>
       <c r="L22" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="N22" t="n">
         <v>0.363</v>
       </c>
       <c r="O22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
         <v>24.8</v>
@@ -4349,13 +4416,13 @@
         <v>34.3</v>
       </c>
       <c r="T22" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
         <v>8.300000000000001</v>
@@ -4367,19 +4434,19 @@
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,16 +4461,16 @@
         <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
       </c>
       <c r="AL22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4415,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4424,10 +4491,10 @@
         <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4448,7 +4515,7 @@
         <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.278</v>
+        <v>0.268</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
@@ -4516,22 +4583,22 @@
         <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P23" t="n">
         <v>20.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.766</v>
+        <v>0.768</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S23" t="n">
         <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
         <v>21</v>
@@ -4540,7 +4607,7 @@
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
@@ -4558,7 +4625,7 @@
         <v>96.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.3</v>
+        <v>-5.5</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4618,7 +4685,7 @@
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4770,7 +4837,7 @@
         <v>20</v>
       </c>
       <c r="AM24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
@@ -4788,7 +4855,7 @@
         <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
@@ -4815,7 +4882,7 @@
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4992,19 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4949,7 +5016,7 @@
         <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4961,7 +5028,7 @@
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
         <v>45</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.625</v>
+        <v>0.634</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J26" t="n">
         <v>87.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
         <v>9.5</v>
@@ -5059,13 +5126,13 @@
         <v>25.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P26" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.82</v>
@@ -5074,16 +5141,16 @@
         <v>12.6</v>
       </c>
       <c r="S26" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T26" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
         <v>5.5</v>
@@ -5098,13 +5165,13 @@
         <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.9</v>
+        <v>107.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -5122,13 +5189,13 @@
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>2</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>6</v>
@@ -5176,7 +5243,7 @@
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,19 +5550,19 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5507,7 +5574,7 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E29" t="n">
         <v>39</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5593,43 +5660,43 @@
         <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
         <v>0.443</v>
       </c>
       <c r="L29" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P29" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T29" t="n">
         <v>43.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W29" t="n">
         <v>7.1</v>
@@ -5638,7 +5705,7 @@
         <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z29" t="n">
         <v>23.1</v>
@@ -5647,13 +5714,13 @@
         <v>22.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
@@ -5662,7 +5729,7 @@
         <v>12</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5677,7 +5744,7 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5692,13 +5759,13 @@
         <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
         <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT29" t="n">
         <v>15</v>
@@ -5707,10 +5774,10 @@
         <v>17</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6062,7 +6129,7 @@
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-25-2013-14</t>
+          <t>2014-03-25</t>
         </is>
       </c>
     </row>
